--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -31,18 +31,19 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -56,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,12 +85,14 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -457,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -483,60 +486,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>결석횟수</t>
+          <t>결석</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>10320</v>
+      <c r="A2" s="1" t="n">
+        <v>10105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>이서준</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+          <t>김윤지</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>주의</t>
         </is>
@@ -545,166 +513,5703 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>10330</v>
+      <c r="A3" s="1" t="n">
+        <v>10109</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>홍길동</t>
+          <t>김효린</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>주의</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>99999</v>
+      <c r="A4" s="1" t="n">
+        <v>10122</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>위험</t>
+          <t>이준서</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>10123</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>전수빈</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>10124</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>조민준</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>10201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>강호윤</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>10206</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>김사랑</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>10208</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>김예찬</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>10223</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>이지호</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10224</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>이현호</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10226</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>장연우</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>10302</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>고현수</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>10305</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>김형진</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>10307</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>문필립</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>10318</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>양별</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>10319</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>이가윤</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>10324</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>임규비</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>10327</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>한준희</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>10328</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>홍정화</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>10406</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>박하빈</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>10411</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>오정현</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>10412</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>오태양</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>10413</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>유동원</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>10416</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>이승빈</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>10417</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>이승욱</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>10418</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>이은유</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>10421</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>장성운</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>10422</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>장유현</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>10423</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>정우영</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>10424</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>정호영</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>10425</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>조윤서</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>10505</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>김성현</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>10506</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>김주원</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>10507</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>김준영</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>10508</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>박민선</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>10509</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>박민제</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>10513</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>성연서</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>10514</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>손유진</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>10515</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>신민</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>10516</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>심예은</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>10517</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>양시현</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>10519</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>오윤재</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>10526</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>최민준</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>10603</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>권다혜</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>10605</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>권유은</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>10609</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>박태희</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>10611</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>손호진</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>10613</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>안주연</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>10618</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>이윤아</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>10623</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>임상혁</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>10624</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>임하연</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>10627</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>정하예</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>10701</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>강석구</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>10704</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>김슬아</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>10705</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>김지아</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>10707</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>박민준</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>10708</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>박성현</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>10709</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>박시온</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>10714</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>이다혜</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>10715</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>이송미</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>10719</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>전범수</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>10720</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>전서현</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>10721</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>정다은</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>10722</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>진서현</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>10724</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>최영재</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>10729</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>윤서은</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>10806</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>김세진</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>10807</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>김종민</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>10817</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>안의민</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>10819</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>오승준</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>10826</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>최찬민</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>20102</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>김서연</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>20103</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>김수인</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>20107</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>박성재</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>20113</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>윤승민</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>20114</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>윤채영</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>20115</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>이가은</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>20117</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>이민영</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>20120</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>정재연</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>20122</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>조유나</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>20124</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>최한비</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>20202</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>김가람</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>20203</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>김규빈</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>20207</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>김태은</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>20208</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>박은선</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>20210</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>서지원</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>20212</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>안준모</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>20215</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>우윤솔</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>20216</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>윤지호</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>20218</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>이수혁</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>20226</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>홍지율</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>20303</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>김동연</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>20312</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>성채현</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>20313</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>송민서</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>20314</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>송치민</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>20316</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>육서연</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>20319</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>이예은</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>20320</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>이지윤</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>20325</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>최현아</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>20326</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>한채호</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>20402</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>김민하</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>20404</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>김채원</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>20405</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>문소윤</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>20406</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>박지후</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>20409</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>송라온</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>20410</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>안장민</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>20414</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>유세현</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>20415</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>유인수</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>20416</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>유희재</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>20423</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>정희주</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>20520</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>송윤주</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>20522</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>이채효</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>20525</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>정지원</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>20526</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>조예진</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>20527</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>최은서</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>20604</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>김예인</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>20605</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>김찬유</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>20606</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>박건우</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>20607</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>박규리</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>20609</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>서예은</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>20614</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>안재현</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>20622</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>장은수</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>20623</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>장현서</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>20704</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>김도담</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>20706</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>김현서</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>20709</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>박준혁</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>20716</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>이상윤</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>20718</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>이재우</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>20724</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>장혜림</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>20725</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>정지우</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>20726</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>조성윤</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>20803</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>20805</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>김연아</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>20806</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>김채린</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>20812</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>박서영</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>20816</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>윤희경</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>20818</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>이소현</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>20821</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>정승헌</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>20823</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>정예준</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>20827</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>홍지유</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>30101</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>김건</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>30102</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>김동건</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>30106</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>김은서</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>30107</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>민경준</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>30115</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>윤승현</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>30116</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>은영진</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>30121</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>장규민</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>30125</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>한채준</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>30126</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>황준현</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>30502</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>강지윤</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>구현우</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>30505</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>박민찬</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>30508</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>백도경</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>30509</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>성기석</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>30513</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>오지수</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>30514</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>윤시연</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>30515</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>이수연</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>30516</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>이승경</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>30519</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>전하민</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>30521</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>최수혁</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>30522</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>최예나</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>30523</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>최인성</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>30525</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>하선우</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>30602</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>김도윤</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>30605</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>명균호</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>30606</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>박성령</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>30614</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>이태민</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>30615</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>임지효</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>30616</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>장리아</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>30618</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>조은찬</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>30625</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>하시헌</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>30701</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>김가현</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>30704</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>김은성</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>30705</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>김지우</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>30708</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>박다니엘</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>30712</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>송원준</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>30714</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>신용우</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>30717</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>윤건희</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>30718</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>이산</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>30719</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>이서현</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>30723</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>조진우</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>30804</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>명예성</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>30805</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>문가영</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>30815</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>유시훈</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>30816</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>유운호</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>30817</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>윤완서</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>30821</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>정채원</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>30823</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>진다민</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>30824</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>최윤서</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>30827</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>황지현</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>30201</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>길나경</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>30204</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>김서준</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>30205</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>김수연</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>30209</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>문서하</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>30212</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>송민우</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>30215</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>오종우</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>30216</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>오주헌</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>30219</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>이제욱</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>30302</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>김동하</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>김주혁</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>30308</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>류승민</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>30313</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>설한나</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>30314</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>송우준</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>30315</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>엄혜준</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>30320</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>이은상</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>30321</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>이준서</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>30323</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>편아윤</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>30326</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>황수현</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>30401</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>강리원</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>30403</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>구은지</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>김민기</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>30406</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>김성주</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>30411</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>박승현</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>30412</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>손규민</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>30414</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>윤서현</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>30423</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>조준성</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>30424</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>최서윤</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>30425</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>최은수</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>30426</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>하지민</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>30427</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>한서정</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
